--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/4TO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXIV/LTAIPT_A63F34D.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/4TO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXIV/LTAIPT_A63F34D.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9c8ec10a61716621/Documentos/CUARTO PAG WEB/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_2B85CC8B652897F07048C45D387B81FC05DAA972" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{535BB4CA-0A35-401E-AC66-D5CCF841291A}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -28,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="384">
   <si>
     <t>49100</t>
   </si>
@@ -285,478 +291,529 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>FC2B1BC02EADC27292EBBDDA8EE83552</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/07/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>Plantel 22 Texoloc</t>
+  </si>
+  <si>
+    <t>Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>Calle</t>
+  </si>
+  <si>
+    <t>Monterrey</t>
+  </si>
+  <si>
+    <t>Sin número</t>
+  </si>
+  <si>
+    <t>s/n</t>
+  </si>
+  <si>
+    <t>Barrio</t>
+  </si>
+  <si>
+    <t>San Damián Texoloc</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>Tlaxcala</t>
+  </si>
+  <si>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>Mexico</t>
+  </si>
+  <si>
+    <t>Urbana</t>
+  </si>
+  <si>
+    <t>Histórico</t>
+  </si>
+  <si>
+    <t>Mixto</t>
+  </si>
+  <si>
+    <t>Educativo</t>
+  </si>
+  <si>
+    <t>Donación</t>
+  </si>
+  <si>
+    <t>11052.9</t>
+  </si>
+  <si>
+    <t>Escritura Pública</t>
+  </si>
+  <si>
+    <t>https://sistemas.indaabin.gob.mx/Inventario_Publico/</t>
+  </si>
+  <si>
+    <t>Departamento de Planeación</t>
+  </si>
+  <si>
+    <t>SUBDIRECCIÓN DE PLANEACIÓN Y EVALUACIÓN INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>Plantel 23 San Pablo del Monte</t>
+  </si>
+  <si>
+    <t>Avenida</t>
+  </si>
+  <si>
+    <t>20 de Noviembre</t>
+  </si>
+  <si>
+    <t>467</t>
+  </si>
+  <si>
+    <t>San Nicolás</t>
+  </si>
+  <si>
+    <t>Villa Vicente Guerrero</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>San Pablo del Monte</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Acta de cabildo de Donación de Predio</t>
+  </si>
+  <si>
+    <t>Plantel 24 Tizatlán</t>
+  </si>
+  <si>
+    <t>Ramón López Velarde</t>
+  </si>
+  <si>
+    <t>Pueblo</t>
+  </si>
+  <si>
+    <t>San Esteban Tizatlan</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>737946.3</t>
+  </si>
+  <si>
+    <t>Dirección Administrativa</t>
+  </si>
+  <si>
+    <t>2 de Abril</t>
+  </si>
+  <si>
+    <t>Colonia</t>
+  </si>
+  <si>
+    <t>Emiliano Zapata</t>
+  </si>
+  <si>
+    <t>Panotla</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>Oficinas</t>
+  </si>
+  <si>
+    <t>Compra-venta</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Copia de Certificado de Propiedad</t>
+  </si>
+  <si>
+    <t>Dirección General</t>
+  </si>
+  <si>
+    <t>Miguel N. Lira</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Centro</t>
+  </si>
+  <si>
+    <t>Tlaxcala de Xicohténcatl</t>
+  </si>
+  <si>
+    <t>Comodato</t>
+  </si>
+  <si>
+    <t>350096.2</t>
+  </si>
+  <si>
+    <t>Ficha Técnica</t>
+  </si>
+  <si>
+    <t>Plantel 01 Tlaxcala</t>
+  </si>
+  <si>
+    <t>Carretera Ocotlán Santa Ana</t>
+  </si>
+  <si>
+    <t>El Sabinal</t>
+  </si>
+  <si>
+    <t>1008141</t>
+  </si>
+  <si>
+    <t>Plantel 02 Huamantla (El Calvario)</t>
+  </si>
+  <si>
+    <t>Francisco I. Madero</t>
+  </si>
+  <si>
+    <t>Fraccionamiento</t>
+  </si>
+  <si>
+    <t>El Calvario</t>
+  </si>
+  <si>
+    <t>Huamantla</t>
+  </si>
+  <si>
+    <t>Plantel 02 Huamantla</t>
+  </si>
+  <si>
+    <t>Boulevard Venustiano Carranza</t>
+  </si>
+  <si>
+    <t>507</t>
+  </si>
+  <si>
+    <t>2154416</t>
+  </si>
+  <si>
+    <t>Plantel 03 Calpulalpan</t>
+  </si>
+  <si>
+    <t>16 de Octubre</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>El Palmar</t>
+  </si>
+  <si>
+    <t>Calpulalpan</t>
+  </si>
+  <si>
+    <t>4812303</t>
+  </si>
+  <si>
+    <t>Plantel 04 Chiautempan</t>
+  </si>
+  <si>
+    <t>Campeche</t>
+  </si>
+  <si>
+    <t>El Alto</t>
+  </si>
+  <si>
+    <t>Santa Ana Chiautempan</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Chiautempan</t>
+  </si>
+  <si>
+    <t>Plantel 05 Panzacola</t>
+  </si>
+  <si>
+    <t>De las industrias</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Panzacola</t>
+  </si>
+  <si>
+    <t>Papalotla</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>Papalotla de Xicohténcatl</t>
+  </si>
+  <si>
+    <t>17164.5</t>
+  </si>
+  <si>
+    <t>Plantel 06 Contla</t>
+  </si>
+  <si>
+    <t>20 de Mayo</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Xopantla</t>
+  </si>
+  <si>
+    <t>Contla</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>Contla de Juan Cuamatzi</t>
+  </si>
+  <si>
+    <t>Plantel 07 Buenavista</t>
+  </si>
+  <si>
+    <t>José María Morelos</t>
+  </si>
+  <si>
+    <t>José María Morelos Buenavista</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>Tlaxco</t>
+  </si>
+  <si>
+    <t>Rústica</t>
+  </si>
+  <si>
+    <t>Ejido</t>
+  </si>
+  <si>
+    <t>20000</t>
+  </si>
+  <si>
+    <t>Constancia de posesión</t>
+  </si>
+  <si>
+    <t>Plantel 08 Ixtacuixtla</t>
+  </si>
+  <si>
+    <t>Boulevard</t>
+  </si>
+  <si>
+    <t>Morelos</t>
+  </si>
+  <si>
+    <t>Villa Mariano Matamoros</t>
+  </si>
+  <si>
+    <t>Ixtacuixtla de Mariano Matamoros</t>
+  </si>
+  <si>
+    <t>Certificado de NO propiedad</t>
+  </si>
+  <si>
+    <t>Plantel 09 Tlaxco</t>
+  </si>
+  <si>
+    <t>5 de Mayo</t>
+  </si>
+  <si>
+    <t>Tlaxco de Morelos</t>
+  </si>
+  <si>
+    <t>50000</t>
+  </si>
+  <si>
+    <t>Plantel 10 Apizaco</t>
+  </si>
+  <si>
+    <t>Ricardo Ortíz García</t>
+  </si>
+  <si>
+    <t>3700</t>
+  </si>
+  <si>
+    <t>Agrícola Covadonga</t>
+  </si>
+  <si>
+    <t>Santa Anita Huiloac</t>
+  </si>
+  <si>
+    <t>Apizaco</t>
+  </si>
+  <si>
+    <t>Plantel 11 Panotla</t>
+  </si>
+  <si>
+    <t>Ejido Totolac</t>
+  </si>
+  <si>
+    <t>Decreto de Expropiación</t>
   </si>
   <si>
     <t>Plantel 12 Santa Cruz</t>
   </si>
   <si>
-    <t>Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>Avenida</t>
-  </si>
-  <si>
-    <t>5 de Mayo</t>
-  </si>
-  <si>
     <t>50</t>
   </si>
   <si>
-    <t>s/n</t>
-  </si>
-  <si>
-    <t>Pueblo</t>
-  </si>
-  <si>
     <t>Santa Cruz Tlaxcala</t>
   </si>
   <si>
     <t>26</t>
   </si>
   <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>Tlaxcala</t>
-  </si>
-  <si>
-    <t>90000</t>
-  </si>
-  <si>
-    <t>Mexico</t>
-  </si>
-  <si>
-    <t>Urbana</t>
-  </si>
-  <si>
-    <t>Histórico</t>
-  </si>
-  <si>
-    <t>Mixto</t>
-  </si>
-  <si>
-    <t>Educativo</t>
-  </si>
-  <si>
-    <t>Donación</t>
+    <t>9593.4</t>
   </si>
   <si>
     <t>10847.22</t>
   </si>
   <si>
-    <t>Decreto de Expropiación</t>
-  </si>
-  <si>
-    <t>https://sistemas.indaabin.gob.mx/Inventario_Publico/</t>
-  </si>
-  <si>
-    <t>Departamento de Planeación</t>
-  </si>
-  <si>
-    <t>Subdirección de Planeación y Evaluación</t>
-  </si>
-  <si>
-    <t>27/01/2023</t>
-  </si>
-  <si>
-    <t>Del periodo del 1 de julio de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no cuenta en el inventario con bienes inmuebles en el extranjero a su cargo ni le han sido asignados conforme a la normatividad aplicable. Además, en expediente el avalúo del inmueble no reporta valor catastral.</t>
-  </si>
-  <si>
-    <t>FB51FA737421997BC9EEC38542897815</t>
-  </si>
-  <si>
-    <t>9593.4</t>
-  </si>
-  <si>
-    <t>Escritura Pública</t>
-  </si>
-  <si>
-    <t>43BC0FA9DE259220E276CDC102067AE5</t>
-  </si>
-  <si>
-    <t>Plantel 11 Panotla</t>
-  </si>
-  <si>
-    <t>Emiliano Zapata</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Ejido Totolac</t>
-  </si>
-  <si>
-    <t>Panotla</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>633EFAD0EDADE6C3D2835E859416164D</t>
-  </si>
-  <si>
-    <t>Plantel 10 Apizaco</t>
-  </si>
-  <si>
-    <t>Calle</t>
-  </si>
-  <si>
-    <t>Ricardo Ortíz García</t>
-  </si>
-  <si>
-    <t>3700</t>
-  </si>
-  <si>
-    <t>Colonia</t>
-  </si>
-  <si>
-    <t>Agrícola Covadonga</t>
-  </si>
-  <si>
-    <t>Santa Anita Huiloac</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Apizaco</t>
-  </si>
-  <si>
-    <t>Ejido</t>
-  </si>
-  <si>
-    <t>Constancia de posesión</t>
-  </si>
-  <si>
-    <t>9591E07C4A9D8A9307E9D28BE6A23BD6</t>
-  </si>
-  <si>
-    <t>Plantel 09 Tlaxco</t>
-  </si>
-  <si>
-    <t>Sin número</t>
-  </si>
-  <si>
-    <t>Tlaxco de Morelos</t>
-  </si>
-  <si>
-    <t>Tlaxco</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>50000</t>
-  </si>
-  <si>
-    <t>17F8BB86407F9DEAF4945B2A568D81C8</t>
-  </si>
-  <si>
-    <t>Plantel 08 Ixtacuixtla</t>
-  </si>
-  <si>
-    <t>Boulevard</t>
-  </si>
-  <si>
-    <t>Morelos</t>
-  </si>
-  <si>
-    <t>Barrio</t>
-  </si>
-  <si>
-    <t>Villa Mariano Matamoros</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>Ixtacuixtla de Mariano Matamoros</t>
-  </si>
-  <si>
-    <t>Certificado de NO propiedad</t>
-  </si>
-  <si>
-    <t>6F7D6F17D2DE484461A7F4EA53EDD04D</t>
-  </si>
-  <si>
-    <t>Plantel 07 Buenavista</t>
-  </si>
-  <si>
-    <t>José María Morelos</t>
-  </si>
-  <si>
-    <t>José María Morelos Buenavista</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>Rústica</t>
-  </si>
-  <si>
-    <t>20000</t>
-  </si>
-  <si>
-    <t>0FB979CB041BC0360240ADDBE29A0E8C</t>
-  </si>
-  <si>
-    <t>Plantel 06 Contla</t>
-  </si>
-  <si>
-    <t>20 de Mayo</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>Xopantla</t>
-  </si>
-  <si>
-    <t>Contla</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>Contla de Juan Cuamatzi</t>
-  </si>
-  <si>
-    <t>Compra-venta</t>
-  </si>
-  <si>
-    <t>0B226D690DEDE20378D45011501E0102</t>
-  </si>
-  <si>
-    <t>Plantel 05 Panzacola</t>
-  </si>
-  <si>
-    <t>De las industrias</t>
-  </si>
-  <si>
-    <t>Panzacola</t>
-  </si>
-  <si>
-    <t>Papalotla</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>Papalotla de Xicohténcatl</t>
-  </si>
-  <si>
-    <t>17164.5</t>
-  </si>
-  <si>
-    <t>B45E11087DDFCF6147EC01A36CEE07F1</t>
-  </si>
-  <si>
-    <t>Plantel 04 Chiautempan</t>
-  </si>
-  <si>
-    <t>Campeche</t>
-  </si>
-  <si>
-    <t>El Alto</t>
-  </si>
-  <si>
-    <t>Santa Ana Chiautempan</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>Chiautempan</t>
-  </si>
-  <si>
-    <t>13EC810FBA69C991CE8145F9DC27E84C</t>
-  </si>
-  <si>
-    <t>Plantel 03 Calpulalpan</t>
-  </si>
-  <si>
-    <t>16 de Octubre</t>
-  </si>
-  <si>
-    <t>El Palmar</t>
-  </si>
-  <si>
-    <t>Calpulalpan</t>
-  </si>
-  <si>
-    <t>4812303</t>
-  </si>
-  <si>
-    <t>803FBFBE3D7588EC7EBE2FBC02491585</t>
-  </si>
-  <si>
-    <t>Plantel 02 Huamantla</t>
-  </si>
-  <si>
-    <t>Boulevard Venustiano Carranza</t>
-  </si>
-  <si>
-    <t>507</t>
-  </si>
-  <si>
-    <t>Huamantla</t>
-  </si>
-  <si>
-    <t>2154416</t>
-  </si>
-  <si>
-    <t>695C7C1C8EB9C96FA3CB75199BC1283F</t>
-  </si>
-  <si>
-    <t>Plantel 02 Huamantla (El Calvario)</t>
-  </si>
-  <si>
-    <t>Francisco I. Madero</t>
-  </si>
-  <si>
-    <t>Fraccionamiento</t>
-  </si>
-  <si>
-    <t>El Calvario</t>
-  </si>
-  <si>
-    <t>38C689D02EE45ED739160C4846368C4C</t>
-  </si>
-  <si>
-    <t>Plantel 01 Tlaxcala</t>
-  </si>
-  <si>
-    <t>Carretera Ocotlán Santa Ana</t>
-  </si>
-  <si>
-    <t>El Sabinal</t>
-  </si>
-  <si>
-    <t>Tlaxcala de Xicohténcatl</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>1008141</t>
-  </si>
-  <si>
-    <t>FB2570DAA88321A11741E936BF613114</t>
-  </si>
-  <si>
-    <t>Dirección General</t>
-  </si>
-  <si>
-    <t>Miguel N. Lira</t>
-  </si>
-  <si>
-    <t>Centro</t>
-  </si>
-  <si>
-    <t>Oficinas</t>
-  </si>
-  <si>
-    <t>Comodato</t>
-  </si>
-  <si>
-    <t>350096.2</t>
-  </si>
-  <si>
-    <t>Ficha Técnica</t>
-  </si>
-  <si>
-    <t>C8F5C0FA3073C57A8C83E98F1D882783</t>
-  </si>
-  <si>
-    <t>Dirección Administrativa</t>
-  </si>
-  <si>
-    <t>2 de Abril</t>
-  </si>
-  <si>
-    <t>Copia de Certificado de Propiedad</t>
-  </si>
-  <si>
-    <t>585EB691134C368CBCA18DE498B61EF7</t>
-  </si>
-  <si>
-    <t>Plantel 24 Tizatlán</t>
-  </si>
-  <si>
-    <t>Ramón López Velarde</t>
-  </si>
-  <si>
-    <t>San Esteban Tizatlan</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>737946.3</t>
-  </si>
-  <si>
-    <t>887148C691C8F91E0FD924BE6546BF30</t>
-  </si>
-  <si>
-    <t>Plantel 23 San Pablo del Monte</t>
-  </si>
-  <si>
-    <t>20 de Noviembre</t>
-  </si>
-  <si>
-    <t>467</t>
-  </si>
-  <si>
-    <t>San Nicolás</t>
-  </si>
-  <si>
-    <t>Villa Vicente Guerrero</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>San Pablo del Monte</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>Acta de cabildo de Donación de Predio</t>
-  </si>
-  <si>
-    <t>14FA679027705580F298C23F3B737A46</t>
-  </si>
-  <si>
-    <t>Plantel 22 Texoloc</t>
-  </si>
-  <si>
-    <t>Monterrey</t>
-  </si>
-  <si>
-    <t>San Damián Texoloc</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>11052.9</t>
-  </si>
-  <si>
-    <t>F83079630CC0C745CB361F1F69FF8280</t>
+    <t>Plantel 13 Papalotla</t>
+  </si>
+  <si>
+    <t>Máximo Rojas</t>
+  </si>
+  <si>
+    <t>San Francisco Papalotla</t>
+  </si>
+  <si>
+    <t>311654.4</t>
+  </si>
+  <si>
+    <t>Plantel 14 Nativitas</t>
+  </si>
+  <si>
+    <t>Bachiller</t>
+  </si>
+  <si>
+    <t>Nativitas</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>Certificado Parcelario Ejidal</t>
+  </si>
+  <si>
+    <t>Plantel 15 Hueyotlipan</t>
+  </si>
+  <si>
+    <t>Benito Juárez</t>
+  </si>
+  <si>
+    <t>San Idelfonso Hueyotlipan</t>
+  </si>
+  <si>
+    <t>Hueyotlipan</t>
+  </si>
+  <si>
+    <t>90882.6</t>
+  </si>
+  <si>
+    <t>Plantel 16 Teolocholco</t>
+  </si>
+  <si>
+    <t>21 de marzo</t>
+  </si>
+  <si>
+    <t>Teolocholco (Segunda sección)</t>
+  </si>
+  <si>
+    <t>Teolocholco</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>1268208</t>
+  </si>
+  <si>
+    <t>Plantel 17 Cuapiaxtla</t>
+  </si>
+  <si>
+    <t>Carretera</t>
+  </si>
+  <si>
+    <t>Carretera Federal Libre 136 Tramo México Veracruz</t>
+  </si>
+  <si>
+    <t>Alta Luz</t>
+  </si>
+  <si>
+    <t>Cuapiaxtla</t>
+  </si>
+  <si>
+    <t>Plantel 18 Atltzayanca</t>
+  </si>
+  <si>
+    <t>Cobat</t>
+  </si>
+  <si>
+    <t>San Antonio</t>
+  </si>
+  <si>
+    <t>Atltzayanca</t>
+  </si>
+  <si>
+    <t>1119.86</t>
+  </si>
+  <si>
+    <t>Plantel 19 Xaloztoc</t>
+  </si>
+  <si>
+    <t>República de Chile</t>
+  </si>
+  <si>
+    <t>Venustiano Carranza</t>
+  </si>
+  <si>
+    <t>Xaloztoc</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>Plantel 20 Ixtenco</t>
+  </si>
+  <si>
+    <t>Juan Ponce de León</t>
+  </si>
+  <si>
+    <t>San Antonio, Seccion uno</t>
+  </si>
+  <si>
+    <t>Ixtenco</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>133344.8</t>
   </si>
   <si>
     <t>Plantel 21 Ayometla</t>
@@ -774,151 +831,97 @@
     <t>4994952.15</t>
   </si>
   <si>
-    <t>487EE98002FFE026B35A1B8EBDF38539</t>
-  </si>
-  <si>
-    <t>Plantel 20 Ixtenco</t>
-  </si>
-  <si>
-    <t>Juan Ponce de León</t>
-  </si>
-  <si>
-    <t>San Antonio, Seccion uno</t>
-  </si>
-  <si>
-    <t>Ixtenco</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>133344.8</t>
-  </si>
-  <si>
-    <t>8F61AF2671C4CFCF7E32174ED6EC9F33</t>
-  </si>
-  <si>
-    <t>Plantel 19 Xaloztoc</t>
-  </si>
-  <si>
-    <t>República de Chile</t>
-  </si>
-  <si>
-    <t>Venustiano Carranza</t>
-  </si>
-  <si>
-    <t>Xaloztoc</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>14A7CB8BC7F141CEB63D06089270E486</t>
-  </si>
-  <si>
-    <t>Plantel 18 Atltzayanca</t>
-  </si>
-  <si>
-    <t>Cobat</t>
-  </si>
-  <si>
-    <t>San Antonio</t>
-  </si>
-  <si>
-    <t>Atltzayanca</t>
-  </si>
-  <si>
-    <t>1119.86</t>
-  </si>
-  <si>
-    <t>5832D86A6E1C05063F8E7D4F1DEB8808</t>
-  </si>
-  <si>
-    <t>Plantel 17 Cuapiaxtla</t>
-  </si>
-  <si>
-    <t>Carretera</t>
-  </si>
-  <si>
-    <t>Carretera Federal Libre 136 Tramo México Veracruz</t>
-  </si>
-  <si>
-    <t>Alta Luz</t>
-  </si>
-  <si>
-    <t>Cuapiaxtla</t>
-  </si>
-  <si>
-    <t>B83DCBFFA4C29367F0CDB88A51CDA24D</t>
-  </si>
-  <si>
-    <t>Plantel 16 Teolocholco</t>
-  </si>
-  <si>
-    <t>21 de marzo</t>
-  </si>
-  <si>
-    <t>Teolocholco (Segunda sección)</t>
-  </si>
-  <si>
-    <t>Teolocholco</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>1268208</t>
-  </si>
-  <si>
-    <t>1EADE9B75F341B043E0CF4BC081A54EC</t>
-  </si>
-  <si>
-    <t>Plantel 15 Hueyotlipan</t>
-  </si>
-  <si>
-    <t>Benito Juárez</t>
-  </si>
-  <si>
-    <t>San Idelfonso Hueyotlipan</t>
-  </si>
-  <si>
-    <t>Hueyotlipan</t>
-  </si>
-  <si>
-    <t>90882.6</t>
-  </si>
-  <si>
-    <t>C48F893075075DFECF45D7D682273B1B</t>
-  </si>
-  <si>
-    <t>Plantel 14 Nativitas</t>
-  </si>
-  <si>
-    <t>Bachiller</t>
-  </si>
-  <si>
-    <t>Nativitas</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>Certificado Parcelario Ejidal</t>
-  </si>
-  <si>
-    <t>F36CB5EB39337DA454F356A0BA97F8C5</t>
-  </si>
-  <si>
-    <t>Plantel 13 Papalotla</t>
-  </si>
-  <si>
-    <t>Máximo Rojas</t>
-  </si>
-  <si>
-    <t>San Francisco Papalotla</t>
-  </si>
-  <si>
-    <t>311654.4</t>
+    <t>9BF79962597A9D2B88410C6F6387EA1F</t>
+  </si>
+  <si>
+    <t>01/07/2023</t>
+  </si>
+  <si>
+    <t>31/12/2023</t>
+  </si>
+  <si>
+    <t>11/01/2024</t>
+  </si>
+  <si>
+    <t>755414052ACF390ED158870F94CF9D7F</t>
+  </si>
+  <si>
+    <t>46CAE37ABBD5F3BD1A6082810F16BABD</t>
+  </si>
+  <si>
+    <t>981808FA62A941D812EBE784C737DE71</t>
+  </si>
+  <si>
+    <t>D78E1951ADF459ACF4DB95602E31C864</t>
+  </si>
+  <si>
+    <t>0785945AD43CD8871288D3C51A8EB908</t>
+  </si>
+  <si>
+    <t>59B07553DCAD33469BCABE34D9D23EDA</t>
+  </si>
+  <si>
+    <t>294733A30A3F680AEFD343D16DEE9B17</t>
+  </si>
+  <si>
+    <t>5D9FF6CF8F5491E37BF698ED6191129B</t>
+  </si>
+  <si>
+    <t>3EEF00C67C158B226C0BF196CB0626A7</t>
+  </si>
+  <si>
+    <t>AAC1C4E297A8CAD14BAE0C695E93C226</t>
+  </si>
+  <si>
+    <t>D0F8554E74DF3B0D66946F33F362DC10</t>
+  </si>
+  <si>
+    <t>EA0E00E197729CB6EF1628E1E7DECBCB</t>
+  </si>
+  <si>
+    <t>3E04BC63409A4A58F25A596A1F5EE18D</t>
+  </si>
+  <si>
+    <t>5BB96282666AE10333E07E5D0BD636F7</t>
+  </si>
+  <si>
+    <t>C9C299288F8F107FF4270DABDD356D3D</t>
+  </si>
+  <si>
+    <t>29A76CB086A942A0B8BA0D5E1F629AEF</t>
+  </si>
+  <si>
+    <t>BAB788EFA31D07D2C10606BDC02D65E1</t>
+  </si>
+  <si>
+    <t>8A6A81D301D0A5161C4606DD3032B37D</t>
+  </si>
+  <si>
+    <t>49E1ED5B4669AFE83DAA18A10262895E</t>
+  </si>
+  <si>
+    <t>29DCACF42AAA6A3ED08454D989A0C316</t>
+  </si>
+  <si>
+    <t>22BACD89C560842707776225BA08B8D3</t>
+  </si>
+  <si>
+    <t>23BFAC969766E83E690AD2A0728BE38D</t>
+  </si>
+  <si>
+    <t>9D5CCEFA25423BB54E1F0C1DFA41DD50</t>
+  </si>
+  <si>
+    <t>08F1D1EB82CDBD954D405205356077CB</t>
+  </si>
+  <si>
+    <t>FBA462361DFD0F7D967F4FFC4D4DD380</t>
+  </si>
+  <si>
+    <t>7A1B3CEF1F4A16A278FBEEA8C31A0D97</t>
+  </si>
+  <si>
+    <t>878F169CC1DB0A45E2B5A4C2F6E2C1D3</t>
   </si>
   <si>
     <t>Privada</t>
@@ -1188,7 +1191,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1284,6 +1287,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -1299,44 +1305,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -1364,14 +1370,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -1399,6 +1422,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1410,175 +1450,151 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AJ35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.42578125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.7109375" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -1613,7 +1629,7 @@
     <col min="33" max="33" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="20" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="255" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
@@ -2016,3082 +2032,3082 @@
     </row>
     <row r="8" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="C8" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="K8" s="2" t="s">
+      <c r="L8" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q8" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="L8" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="O8" s="2" t="s">
+      <c r="R8" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="S8" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="P8" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q8" s="2" t="s">
+      <c r="T8" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="R8" s="2" t="s">
+      <c r="U8" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="W8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X8" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="S8" s="2" t="s">
+      <c r="Y8" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="T8" s="2" t="s">
+      <c r="Z8" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="U8" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="V8" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="W8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="X8" s="2" t="s">
+      <c r="AA8" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="Y8" s="2" t="s">
+      <c r="AB8" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="Z8" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA8" s="2" t="s">
+      <c r="AC8" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="AD8" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="AB8" s="2" t="s">
+      <c r="AE8" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="AC8" s="2" t="s">
+      <c r="AF8" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="AD8" s="2" t="s">
+      <c r="AG8" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="AE8" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="AF8" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="AG8" s="2" t="s">
-        <v>111</v>
-      </c>
       <c r="AH8" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AI8" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AJ8" s="2" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>114</v>
+        <v>269</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F9" s="2" t="s">
+      <c r="H9" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="J9" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="K9" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="K9" s="2" t="s">
+      <c r="L9" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q9" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="L9" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="O9" s="2" t="s">
+      <c r="R9" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="S9" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="P9" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q9" s="2" t="s">
+      <c r="T9" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="R9" s="2" t="s">
+      <c r="U9" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="W9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X9" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="S9" s="2" t="s">
+      <c r="Y9" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="T9" s="2" t="s">
+      <c r="Z9" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="U9" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="V9" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="W9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="X9" s="2" t="s">
+      <c r="AA9" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="Y9" s="2" t="s">
+      <c r="AB9" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="Z9" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA9" s="2" t="s">
+      <c r="AC9" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="AD9" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="AB9" s="2" t="s">
+      <c r="AE9" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="AC9" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="AD9" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="AE9" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="AF9" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AG9" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AH9" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AI9" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AJ9" s="2" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>117</v>
+        <v>270</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="F10" s="2" t="s">
+      <c r="H10" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="J10" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="K10" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q10" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="L10" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q10" s="2" t="s">
+      <c r="R10" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T10" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="R10" s="2" t="s">
+      <c r="U10" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="V10" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="W10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X10" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="S10" s="2" t="s">
+      <c r="Y10" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="T10" s="2" t="s">
+      <c r="Z10" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="U10" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="V10" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="W10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="X10" s="2" t="s">
+      <c r="AA10" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="Y10" s="2" t="s">
+      <c r="AB10" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="Z10" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA10" s="2" t="s">
+      <c r="AC10" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="AD10" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="AB10" s="2" t="s">
+      <c r="AE10" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="AC10" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="AD10" s="2" t="s">
+      <c r="AF10" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AG10" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="AE10" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="AF10" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="AG10" s="2" t="s">
-        <v>111</v>
-      </c>
       <c r="AH10" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AI10" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AJ10" s="2" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>125</v>
+        <v>271</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="F11" s="2" t="s">
+      <c r="H11" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="H11" s="2" t="s">
+      <c r="J11" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="K11" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="I11" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="L11" s="2" t="s">
-        <v>131</v>
+        <v>251</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>132</v>
+        <v>252</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>133</v>
+        <v>253</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>134</v>
+        <v>252</v>
       </c>
       <c r="Q11" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T11" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="R11" s="2" t="s">
+      <c r="U11" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="V11" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="W11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X11" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="S11" s="2" t="s">
+      <c r="Y11" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="T11" s="2" t="s">
+      <c r="Z11" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="U11" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="V11" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="W11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="X11" s="2" t="s">
+      <c r="AA11" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="Y11" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="Z11" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA11" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="AB11" s="2" t="s">
-        <v>135</v>
+        <v>191</v>
       </c>
       <c r="AC11" s="2" t="s">
-        <v>124</v>
+        <v>6</v>
       </c>
       <c r="AD11" s="2" t="s">
-        <v>136</v>
+        <v>193</v>
       </c>
       <c r="AE11" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="AF11" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AG11" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AH11" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AI11" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AJ11" s="2" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>137</v>
+        <v>272</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="G12" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F12" s="2" t="s">
+      <c r="H12" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>139</v>
-      </c>
       <c r="J12" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>140</v>
+        <v>262</v>
       </c>
       <c r="M12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>141</v>
+        <v>262</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>142</v>
+        <v>263</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>141</v>
+        <v>262</v>
       </c>
       <c r="Q12" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T12" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="R12" s="2" t="s">
+      <c r="U12" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="V12" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="W12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X12" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="S12" s="2" t="s">
+      <c r="Y12" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="T12" s="2" t="s">
+      <c r="Z12" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="U12" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="V12" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="W12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="X12" s="2" t="s">
+      <c r="AA12" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="Y12" s="2" t="s">
+      <c r="AB12" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="Z12" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA12" s="2" t="s">
+      <c r="AC12" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="AD12" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="AB12" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="AC12" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="AD12" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="AE12" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="AF12" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AG12" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AH12" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AI12" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AJ12" s="2" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>144</v>
+        <v>273</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F13" s="2" t="s">
+      <c r="G13" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>139</v>
-      </c>
       <c r="J13" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>148</v>
+        <v>92</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>149</v>
+        <v>256</v>
       </c>
       <c r="M13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>149</v>
+        <v>257</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>150</v>
+        <v>258</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>151</v>
+        <v>257</v>
       </c>
       <c r="Q13" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T13" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="R13" s="2" t="s">
+      <c r="U13" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="V13" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="W13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X13" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="S13" s="2" t="s">
+      <c r="Y13" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="T13" s="2" t="s">
+      <c r="Z13" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="U13" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="V13" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="W13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="X13" s="2" t="s">
+      <c r="AA13" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="Y13" s="2" t="s">
+      <c r="AB13" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="Z13" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA13" s="2" t="s">
+      <c r="AC13" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="AD13" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="AB13" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="AC13" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="AD13" s="2" t="s">
-        <v>152</v>
-      </c>
       <c r="AE13" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="AF13" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AG13" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AH13" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AI13" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AJ13" s="2" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>153</v>
+        <v>274</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="G14" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="F14" s="2" t="s">
+      <c r="H14" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G14" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>139</v>
-      </c>
       <c r="J14" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="O14" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="K14" s="2" t="s">
+      <c r="P14" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q14" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="L14" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="P14" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="Q14" s="2" t="s">
+      <c r="R14" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T14" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="R14" s="2" t="s">
+      <c r="U14" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="V14" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="W14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X14" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="S14" s="2" t="s">
+      <c r="Y14" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="T14" s="2" t="s">
+      <c r="Z14" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="U14" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="V14" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="W14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="X14" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="Y14" s="2" t="s">
+      <c r="AA14" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AB14" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="Z14" s="2" t="s">
+      <c r="AC14" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="AA14" s="2" t="s">
+      <c r="AD14" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="AB14" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="AC14" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="AD14" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="AE14" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="AF14" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AG14" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AH14" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AI14" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AJ14" s="2" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>160</v>
+        <v>275</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="G15" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="F15" s="2" t="s">
+      <c r="H15" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G15" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>163</v>
-      </c>
       <c r="J15" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>164</v>
+        <v>122</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>6</v>
+        <v>123</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>165</v>
+        <v>122</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>166</v>
+        <v>124</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>167</v>
+        <v>96</v>
       </c>
       <c r="Q15" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T15" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="R15" s="2" t="s">
+      <c r="U15" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="V15" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="W15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X15" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="S15" s="2" t="s">
+      <c r="Y15" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="T15" s="2" t="s">
+      <c r="Z15" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="U15" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="V15" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="W15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="X15" s="2" t="s">
+      <c r="AA15" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="Y15" s="2" t="s">
+      <c r="AB15" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="Z15" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA15" s="2" t="s">
+      <c r="AC15" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AD15" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="AB15" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="AC15" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="AD15" s="2" t="s">
-        <v>116</v>
-      </c>
       <c r="AE15" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="AF15" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AG15" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AH15" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AI15" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AJ15" s="2" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>169</v>
+        <v>276</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="G16" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="J16" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="H16" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="K16" s="2" t="s">
-        <v>130</v>
+        <v>92</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>172</v>
+        <v>113</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>173</v>
+        <v>114</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>174</v>
+        <v>115</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>175</v>
+        <v>116</v>
       </c>
       <c r="Q16" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T16" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="R16" s="2" t="s">
+      <c r="U16" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="V16" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="W16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X16" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="S16" s="2" t="s">
+      <c r="Y16" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="T16" s="2" t="s">
+      <c r="Z16" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="U16" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="V16" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="W16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="X16" s="2" t="s">
+      <c r="AA16" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="Y16" s="2" t="s">
+      <c r="AB16" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="Z16" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA16" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="AB16" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="AC16" s="2" t="s">
-        <v>176</v>
+        <v>117</v>
       </c>
       <c r="AD16" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AE16" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="AF16" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AG16" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AH16" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AI16" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AJ16" s="2" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>177</v>
+        <v>277</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="G17" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="F17" s="2" t="s">
+      <c r="H17" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="J17" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="H17" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="K17" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N17" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="L17" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>181</v>
-      </c>
       <c r="O17" s="2" t="s">
-        <v>182</v>
+        <v>131</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>183</v>
+        <v>130</v>
       </c>
       <c r="Q17" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T17" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="R17" s="2" t="s">
+      <c r="U17" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="V17" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="W17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X17" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="S17" s="2" t="s">
+      <c r="Y17" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="T17" s="2" t="s">
+      <c r="Z17" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="U17" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="V17" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="W17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="X17" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Y17" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="Z17" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="AA17" s="2" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="AB17" s="2" t="s">
-        <v>168</v>
+        <v>133</v>
       </c>
       <c r="AC17" s="2" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="AD17" s="2" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="AE17" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="AF17" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AG17" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AH17" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AI17" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AJ17" s="2" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>184</v>
+        <v>278</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="G18" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F18" s="2" t="s">
+      <c r="H18" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G18" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>150</v>
-      </c>
       <c r="J18" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>187</v>
+        <v>146</v>
       </c>
       <c r="M18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>188</v>
+        <v>140</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>10</v>
+        <v>124</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>188</v>
+        <v>96</v>
       </c>
       <c r="Q18" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T18" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="R18" s="2" t="s">
+      <c r="U18" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="V18" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="W18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X18" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="S18" s="2" t="s">
+      <c r="Y18" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="T18" s="2" t="s">
+      <c r="Z18" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="U18" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="V18" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="W18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="X18" s="2" t="s">
+      <c r="AA18" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="Y18" s="2" t="s">
+      <c r="AB18" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="Z18" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA18" s="2" t="s">
+      <c r="AC18" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="AD18" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="AB18" s="2" t="s">
+      <c r="AE18" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="AC18" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="AD18" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="AE18" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="AF18" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AG18" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AH18" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AI18" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AJ18" s="2" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>190</v>
+        <v>279</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="G19" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="H19" s="2" t="s">
-        <v>192</v>
+        <v>137</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>193</v>
+        <v>138</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="M19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>194</v>
+        <v>140</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>12</v>
+        <v>124</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>194</v>
+        <v>96</v>
       </c>
       <c r="Q19" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T19" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="R19" s="2" t="s">
+      <c r="U19" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="V19" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="W19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X19" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="S19" s="2" t="s">
+      <c r="Y19" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="T19" s="2" t="s">
+      <c r="Z19" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="U19" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="V19" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="W19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="X19" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Y19" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="Z19" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="AA19" s="2" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="AB19" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="AC19" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="AD19" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="AE19" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="AC19" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="AD19" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="AE19" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="AF19" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AG19" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AH19" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AI19" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AJ19" s="2" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>196</v>
+        <v>280</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="G20" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="F20" s="2" t="s">
+      <c r="H20" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G20" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>139</v>
-      </c>
       <c r="J20" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>200</v>
+        <v>151</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>6</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>194</v>
+        <v>152</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>12</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>194</v>
+        <v>152</v>
       </c>
       <c r="Q20" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T20" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="R20" s="2" t="s">
+      <c r="U20" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="V20" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="W20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X20" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="S20" s="2" t="s">
+      <c r="Y20" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="T20" s="2" t="s">
+      <c r="Z20" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="U20" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="V20" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="W20" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="X20" s="2" t="s">
+      <c r="AA20" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="Y20" s="2" t="s">
+      <c r="AB20" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="Z20" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA20" s="2" t="s">
+      <c r="AC20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD20" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="AB20" s="2" t="s">
+      <c r="AE20" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="AC20" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="AD20" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="AE20" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="AF20" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AG20" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AH20" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AI20" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AJ20" s="2" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>201</v>
+        <v>281</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="G21" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="H21" s="2" t="s">
-        <v>203</v>
+        <v>158</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>204</v>
+        <v>160</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>6</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>205</v>
+        <v>161</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>206</v>
+        <v>10</v>
       </c>
       <c r="P21" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T21" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="U21" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="V21" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="W21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X21" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="Q21" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="R21" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="S21" s="2" t="s">
+      <c r="Y21" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="T21" s="2" t="s">
+      <c r="Z21" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="U21" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="V21" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="W21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="X21" s="2" t="s">
+      <c r="AA21" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="Y21" s="2" t="s">
+      <c r="AB21" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="Z21" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA21" s="2" t="s">
+      <c r="AC21" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="AD21" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="AB21" s="2" t="s">
+      <c r="AE21" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="AC21" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="AD21" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="AE21" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="AF21" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AG21" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AH21" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AI21" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AJ21" s="2" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>208</v>
+        <v>282</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="G22" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="H22" s="2" t="s">
-        <v>210</v>
+        <v>154</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>120</v>
+        <v>155</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>211</v>
+        <v>129</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>6</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>205</v>
+        <v>152</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>206</v>
+        <v>12</v>
       </c>
       <c r="P22" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T22" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="U22" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="V22" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="W22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X22" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="Q22" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="R22" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="S22" s="2" t="s">
+      <c r="Y22" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="T22" s="2" t="s">
+      <c r="Z22" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="U22" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="V22" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="W22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="X22" s="2" t="s">
+      <c r="AA22" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="Y22" s="2" t="s">
+      <c r="AB22" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="Z22" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA22" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="AB22" s="2" t="s">
-        <v>213</v>
-      </c>
       <c r="AC22" s="2" t="s">
-        <v>214</v>
+        <v>156</v>
       </c>
       <c r="AD22" s="2" t="s">
-        <v>215</v>
+        <v>105</v>
       </c>
       <c r="AE22" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="AF22" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AG22" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AH22" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AI22" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AJ22" s="2" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>216</v>
+        <v>283</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="F23" s="2" t="s">
+      <c r="G23" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G23" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>139</v>
-      </c>
       <c r="J23" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>119</v>
+        <v>165</v>
       </c>
       <c r="M23" s="2" t="s">
         <v>6</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>122</v>
+        <v>166</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>123</v>
+        <v>167</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>122</v>
+        <v>168</v>
       </c>
       <c r="Q23" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T23" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="R23" s="2" t="s">
+      <c r="U23" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="V23" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="W23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X23" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="S23" s="2" t="s">
+      <c r="Y23" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="T23" s="2" t="s">
+      <c r="Z23" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="U23" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="V23" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="W23" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="X23" s="2" t="s">
+      <c r="AA23" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="Y23" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="Z23" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA23" s="2" t="s">
-        <v>212</v>
-      </c>
       <c r="AB23" s="2" t="s">
-        <v>168</v>
+        <v>133</v>
       </c>
       <c r="AC23" s="2" t="s">
-        <v>124</v>
+        <v>6</v>
       </c>
       <c r="AD23" s="2" t="s">
-        <v>219</v>
+        <v>105</v>
       </c>
       <c r="AE23" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="AF23" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AG23" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AH23" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AI23" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AJ23" s="2" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>220</v>
+        <v>284</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="G24" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="H24" s="2" t="s">
-        <v>222</v>
+        <v>178</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>139</v>
+        <v>179</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K24" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q24" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="L24" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="M24" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="N24" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="O24" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="P24" s="2" t="s">
+      <c r="R24" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T24" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="U24" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="V24" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="W24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X24" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="Q24" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="R24" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="S24" s="2" t="s">
+      <c r="Y24" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="T24" s="2" t="s">
+      <c r="Z24" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="U24" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="V24" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="W24" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="X24" s="2" t="s">
+      <c r="AA24" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="Y24" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="Z24" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA24" s="2" t="s">
+      <c r="AB24" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AC24" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="AD24" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="AB24" s="2" t="s">
+      <c r="AE24" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="AC24" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="AD24" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="AE24" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="AF24" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AG24" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AH24" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AI24" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AJ24" s="2" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>226</v>
+        <v>285</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="G25" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J25" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="H25" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="K25" s="2" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="M25" s="2" t="s">
         <v>6</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>231</v>
+        <v>173</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>232</v>
+        <v>174</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>233</v>
+        <v>175</v>
       </c>
       <c r="Q25" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T25" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="R25" s="2" t="s">
+      <c r="U25" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="V25" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="W25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X25" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="S25" s="2" t="s">
+      <c r="Y25" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="T25" s="2" t="s">
+      <c r="Z25" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="U25" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="V25" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="W25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="X25" s="2" t="s">
+      <c r="AA25" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="Y25" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="Z25" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA25" s="2" t="s">
+      <c r="AB25" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AC25" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="AD25" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="AB25" s="2" t="s">
+      <c r="AE25" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="AC25" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="AD25" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="AE25" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="AF25" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AG25" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AH25" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AI25" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AJ25" s="2" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>236</v>
+        <v>286</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="G26" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="F26" s="2" t="s">
+      <c r="H26" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G26" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>139</v>
-      </c>
       <c r="J26" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>238</v>
+        <v>186</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>6</v>
+        <v>187</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>239</v>
+        <v>186</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>240</v>
+        <v>188</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>239</v>
+        <v>189</v>
       </c>
       <c r="Q26" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R26" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="S26" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T26" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="R26" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="S26" s="2" t="s">
+      <c r="U26" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="V26" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="W26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X26" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="Y26" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="T26" s="2" t="s">
+      <c r="Z26" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="U26" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="V26" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="W26" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="X26" s="2" t="s">
+      <c r="AA26" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="Y26" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="Z26" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA26" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="AB26" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="AC26" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="AD26" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="AE26" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="AC26" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="AD26" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="AE26" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="AF26" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AG26" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AH26" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AI26" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AJ26" s="2" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>242</v>
+        <v>287</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="G27" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="F27" s="2" t="s">
+      <c r="H27" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G27" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>139</v>
-      </c>
       <c r="J27" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K27" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q27" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="L27" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="M27" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="N27" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="O27" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="P27" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="Q27" s="2" t="s">
+      <c r="R27" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="S27" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T27" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="R27" s="2" t="s">
+      <c r="U27" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="V27" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="W27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X27" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="S27" s="2" t="s">
+      <c r="Y27" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="T27" s="2" t="s">
+      <c r="Z27" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="U27" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="V27" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="W27" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="X27" s="2" t="s">
+      <c r="AA27" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="Y27" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="Z27" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA27" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="AB27" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="AC27" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="AD27" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="AE27" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="AC27" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="AD27" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="AE27" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="AF27" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AG27" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AH27" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AI27" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AJ27" s="2" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>248</v>
+        <v>288</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="F28" s="2" t="s">
+      <c r="G28" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="J28" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="H28" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="K28" s="2" t="s">
-        <v>148</v>
+        <v>92</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>251</v>
+        <v>197</v>
       </c>
       <c r="M28" s="2" t="s">
         <v>6</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>252</v>
+        <v>197</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>253</v>
+        <v>159</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>252</v>
+        <v>198</v>
       </c>
       <c r="Q28" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R28" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="S28" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T28" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="R28" s="2" t="s">
+      <c r="U28" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="V28" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="W28" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X28" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="S28" s="2" t="s">
+      <c r="Y28" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="T28" s="2" t="s">
+      <c r="Z28" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="U28" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="V28" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="W28" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="X28" s="2" t="s">
+      <c r="AA28" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="Y28" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="Z28" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA28" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="AB28" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="AC28" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD28" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="AE28" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="AC28" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="AD28" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="AE28" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="AF28" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AG28" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AH28" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AI28" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AJ28" s="2" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>255</v>
+        <v>289</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="G29" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="H29" s="2" t="s">
-        <v>257</v>
+        <v>205</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>139</v>
+        <v>206</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>258</v>
+        <v>207</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>259</v>
+        <v>208</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>260</v>
+        <v>171</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>259</v>
+        <v>209</v>
       </c>
       <c r="Q29" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R29" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="S29" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T29" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="R29" s="2" t="s">
+      <c r="U29" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="V29" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="W29" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X29" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="S29" s="2" t="s">
+      <c r="Y29" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="T29" s="2" t="s">
+      <c r="Z29" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="U29" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="V29" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="W29" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="X29" s="2" t="s">
+      <c r="AA29" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="Y29" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="Z29" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA29" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="AB29" s="2" t="s">
-        <v>135</v>
+        <v>191</v>
       </c>
       <c r="AC29" s="2" t="s">
-        <v>124</v>
+        <v>6</v>
       </c>
       <c r="AD29" s="2" t="s">
-        <v>136</v>
+        <v>193</v>
       </c>
       <c r="AE29" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="AF29" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AG29" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AH29" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AI29" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AJ29" s="2" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>261</v>
+        <v>290</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="G30" s="2" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>263</v>
+        <v>201</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>139</v>
+        <v>214</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>264</v>
+        <v>215</v>
       </c>
       <c r="M30" s="2" t="s">
         <v>6</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>265</v>
+        <v>215</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>7</v>
+        <v>216</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>265</v>
+        <v>215</v>
       </c>
       <c r="Q30" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R30" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="S30" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T30" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="R30" s="2" t="s">
+      <c r="U30" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="V30" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="W30" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X30" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="S30" s="2" t="s">
+      <c r="Y30" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="T30" s="2" t="s">
+      <c r="Z30" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="U30" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="V30" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="W30" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="X30" s="2" t="s">
+      <c r="AA30" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="Y30" s="2" t="s">
+      <c r="AB30" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="Z30" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA30" s="2" t="s">
+      <c r="AC30" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="AD30" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="AB30" s="2" t="s">
+      <c r="AE30" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="AC30" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="AD30" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="AE30" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="AF30" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AG30" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AH30" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AI30" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AJ30" s="2" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C31" s="2" t="s">
+      <c r="E31" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F31" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="G31" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q31" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R31" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="S31" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T31" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="U31" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="V31" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="W31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X31" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y31" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z31" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AA31" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AB31" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AC31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD31" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="AE31" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="AF31" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AG31" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AH31" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="F31" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="M31" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="N31" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="O31" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="P31" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="Q31" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="R31" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="S31" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="T31" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="U31" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="V31" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="W31" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="X31" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Y31" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="Z31" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA31" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="AB31" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="AC31" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="AD31" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="AE31" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="AF31" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="AG31" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="AH31" s="2" t="s">
-        <v>112</v>
-      </c>
       <c r="AI31" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AJ31" s="2" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>273</v>
+        <v>292</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C32" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F32" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="G32" s="2" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>275</v>
+        <v>201</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>139</v>
+        <v>214</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>276</v>
+        <v>215</v>
       </c>
       <c r="M32" s="2" t="s">
         <v>6</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>277</v>
+        <v>215</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>278</v>
+        <v>216</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>277</v>
+        <v>215</v>
       </c>
       <c r="Q32" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R32" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="S32" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T32" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="R32" s="2" t="s">
+      <c r="U32" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="V32" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="W32" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X32" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="S32" s="2" t="s">
+      <c r="Y32" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="T32" s="2" t="s">
+      <c r="Z32" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="U32" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="V32" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="W32" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="X32" s="2" t="s">
+      <c r="AA32" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="Y32" s="2" t="s">
+      <c r="AB32" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="Z32" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA32" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="AB32" s="2" t="s">
+      <c r="AC32" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="AD32" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="AE32" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="AC32" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="AD32" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="AE32" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="AF32" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AG32" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AH32" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AI32" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AJ32" s="2" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C33" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F33" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="F33" s="2" t="s">
+      <c r="G33" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="I33" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="J33" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="H33" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="K33" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N33" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="O33" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q33" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="L33" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="M33" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="N33" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="O33" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="P33" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="Q33" s="2" t="s">
+      <c r="R33" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="S33" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T33" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="R33" s="2" t="s">
+      <c r="U33" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="V33" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="W33" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X33" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="S33" s="2" t="s">
+      <c r="Y33" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="T33" s="2" t="s">
+      <c r="Z33" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="U33" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="V33" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="W33" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="X33" s="2" t="s">
+      <c r="AA33" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="Y33" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="Z33" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA33" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="AB33" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="AC33" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="AD33" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="AE33" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="AC33" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="AD33" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="AE33" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="AF33" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AG33" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AH33" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AI33" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AJ33" s="2" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C34" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F34" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="F34" s="2" t="s">
+      <c r="G34" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="I34" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="J34" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="H34" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="K34" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N34" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="O34" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="P34" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q34" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="L34" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="M34" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="N34" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="O34" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="P34" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="Q34" s="2" t="s">
+      <c r="R34" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="S34" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T34" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="R34" s="2" t="s">
+      <c r="U34" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="V34" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="W34" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X34" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="S34" s="2" t="s">
+      <c r="Y34" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="T34" s="2" t="s">
+      <c r="Z34" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="U34" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="V34" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="W34" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="X34" s="2" t="s">
+      <c r="AA34" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="Y34" s="2" t="s">
+      <c r="AB34" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="Z34" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA34" s="2" t="s">
+      <c r="AC34" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="AD34" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="AB34" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="AC34" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="AD34" s="2" t="s">
-        <v>291</v>
-      </c>
       <c r="AE34" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="AF34" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AG34" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AH34" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AI34" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AJ34" s="2" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C35" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F35" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="F35" s="2" t="s">
+      <c r="G35" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="I35" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="J35" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="H35" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="K35" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N35" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="O35" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q35" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="L35" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="M35" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="N35" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="O35" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="P35" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q35" s="2" t="s">
+      <c r="R35" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="S35" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T35" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="R35" s="2" t="s">
+      <c r="U35" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="V35" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="W35" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X35" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="S35" s="2" t="s">
+      <c r="Y35" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="T35" s="2" t="s">
+      <c r="Z35" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="U35" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="V35" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="W35" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="X35" s="2" t="s">
+      <c r="AA35" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="Y35" s="2" t="s">
+      <c r="AB35" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="Z35" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA35" s="2" t="s">
+      <c r="AC35" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="AD35" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="AB35" s="2" t="s">
+      <c r="AE35" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="AC35" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="AD35" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="AE35" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="AF35" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AG35" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AH35" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AI35" s="2" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AJ35" s="2" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -5105,22 +5121,22 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G8:G140">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G8:G173" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Hidden_16</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K8:K140">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K8:K173" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>Hidden_210</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R8:R140">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R8:R173" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>Hidden_317</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="X8:X140">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="X8:X173" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>Hidden_423</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Y8:Y140">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Y8:Y173" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>Hidden_524</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Z8:Z140">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Z8:Z173" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>Hidden_625</formula1>
     </dataValidation>
   </dataValidations>
@@ -5129,138 +5145,138 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>269</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>127</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>146</v>
+        <v>195</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -5269,213 +5285,213 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>148</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>135</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>199</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>95</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -5484,168 +5500,168 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>147</v>
+        <v>196</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
   </sheetData>
@@ -5654,18 +5670,18 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>158</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -5674,23 +5690,23 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -5699,23 +5715,23 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
